--- a/public/shopee-template.xlsx
+++ b/public/shopee-template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="425">
   <si>
     <t>et_title_product_id</t>
   </si>
@@ -153,19 +153,85 @@
     <t>Benang Obras Ivory 2 Ons Kategori Pink | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>446245042489</t>
+  </si>
+  <si>
+    <t>R174 Dusty Pink</t>
+  </si>
+  <si>
+    <t>12999</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>446245042478</t>
+  </si>
+  <si>
+    <t>8057 Salem</t>
+  </si>
+  <si>
+    <t>446245042476</t>
+  </si>
+  <si>
+    <t>4584 Dusty Pink</t>
+  </si>
+  <si>
+    <t>446245042482</t>
+  </si>
+  <si>
+    <t>R511 Dusty Pink Tua</t>
+  </si>
+  <si>
+    <t>446245042485</t>
+  </si>
+  <si>
+    <t>2051 Salem</t>
+  </si>
+  <si>
+    <t>446245042486</t>
+  </si>
+  <si>
+    <t>9299 Baby Pink</t>
+  </si>
+  <si>
+    <t>446245042477</t>
+  </si>
+  <si>
+    <t>8969 Rose Pink</t>
+  </si>
+  <si>
     <t>446245042483</t>
   </si>
   <si>
     <t>334 Peach</t>
   </si>
   <si>
-    <t>12999</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>446245042480</t>
+  </si>
+  <si>
+    <t>171B Cherry Blossom</t>
+  </si>
+  <si>
+    <t>446245042475</t>
+  </si>
+  <si>
+    <t>501 Dusty Pink</t>
+  </si>
+  <si>
+    <t>446245042487</t>
+  </si>
+  <si>
+    <t>2052 Coral</t>
+  </si>
+  <si>
+    <t>446245042490</t>
+  </si>
+  <si>
+    <t>2201 Pink</t>
   </si>
   <si>
     <t>446245042481</t>
@@ -174,102 +240,228 @@
     <t>9052 Coral</t>
   </si>
   <si>
-    <t>446245042487</t>
-  </si>
-  <si>
-    <t>2052 Coral</t>
-  </si>
-  <si>
-    <t>446245042482</t>
-  </si>
-  <si>
-    <t>R511 Dusty Pink Tua</t>
-  </si>
-  <si>
     <t>446245042479</t>
   </si>
   <si>
     <t>014 WaterMelon</t>
   </si>
   <si>
-    <t>446245042489</t>
-  </si>
-  <si>
-    <t>R174 Dusty Pink</t>
-  </si>
-  <si>
-    <t>446245042478</t>
-  </si>
-  <si>
-    <t>8057 Salem</t>
-  </si>
-  <si>
-    <t>446245042485</t>
-  </si>
-  <si>
-    <t>2051 Salem</t>
-  </si>
-  <si>
     <t>446245042484</t>
   </si>
   <si>
     <t>826 Pink Cerise</t>
   </si>
   <si>
+    <t>446245042474</t>
+  </si>
+  <si>
+    <t>723 Dusty Pink Muda</t>
+  </si>
+  <si>
     <t>446245042488</t>
   </si>
   <si>
     <t>2056 Pink Muda</t>
   </si>
   <si>
-    <t>446245042490</t>
-  </si>
-  <si>
-    <t>2201 Pink</t>
-  </si>
-  <si>
-    <t>446245042476</t>
-  </si>
-  <si>
-    <t>4584 Dusty Pink</t>
-  </si>
-  <si>
-    <t>446245042480</t>
-  </si>
-  <si>
-    <t>171B Cherry Blossom</t>
-  </si>
-  <si>
-    <t>446245042474</t>
-  </si>
-  <si>
-    <t>723 Dusty Pink Muda</t>
-  </si>
-  <si>
-    <t>446245042486</t>
-  </si>
-  <si>
-    <t>9299 Baby Pink</t>
-  </si>
-  <si>
-    <t>446245042477</t>
-  </si>
-  <si>
-    <t>8969 Rose Pink</t>
-  </si>
-  <si>
-    <t>446245042475</t>
-  </si>
-  <si>
-    <t>501 Dusty Pink</t>
-  </si>
-  <si>
     <t>55713028154</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Biru | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>351130045994</t>
+  </si>
+  <si>
+    <t>138 Biru Muda</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>351130045988</t>
+  </si>
+  <si>
+    <t>035 Biru Tua</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>351130045984</t>
+  </si>
+  <si>
+    <t>R274 Biru Russian</t>
+  </si>
+  <si>
+    <t>R274</t>
+  </si>
+  <si>
+    <t>351130045986</t>
+  </si>
+  <si>
+    <t>9085 Biru Langit</t>
+  </si>
+  <si>
+    <t>9085</t>
+  </si>
+  <si>
+    <t>351130046001</t>
+  </si>
+  <si>
+    <t>055 Biru Navy</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>351130046003</t>
+  </si>
+  <si>
+    <t>R532 Biru Emerld</t>
+  </si>
+  <si>
+    <t>R532</t>
+  </si>
+  <si>
+    <t>351130045992</t>
+  </si>
+  <si>
+    <t>8049 Baby Blue</t>
+  </si>
+  <si>
+    <t>8049</t>
+  </si>
+  <si>
+    <t>351130045998</t>
+  </si>
+  <si>
+    <t>CB Turkish Tua</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>351130045983</t>
+  </si>
+  <si>
+    <t>2084 Biru Langit</t>
+  </si>
+  <si>
+    <t>2084</t>
+  </si>
+  <si>
+    <t>351130045990</t>
+  </si>
+  <si>
+    <t>R530 Dusty Blue</t>
+  </si>
+  <si>
+    <t>R530</t>
+  </si>
+  <si>
+    <t>351130045991</t>
+  </si>
+  <si>
+    <t>R205 Biru Emerlad</t>
+  </si>
+  <si>
+    <t>R205</t>
+  </si>
+  <si>
+    <t>351130045993</t>
+  </si>
+  <si>
+    <t>8080 Blue</t>
+  </si>
+  <si>
+    <t>8080</t>
+  </si>
+  <si>
+    <t>351130045996</t>
+  </si>
+  <si>
+    <t>8805 Biru Turkis</t>
+  </si>
+  <si>
+    <t>8805</t>
+  </si>
+  <si>
+    <t>351130045997</t>
+  </si>
+  <si>
+    <t>R533 Biru pearl</t>
+  </si>
+  <si>
+    <t>R533</t>
+  </si>
+  <si>
+    <t>351130045995</t>
+  </si>
+  <si>
+    <t>R379 Biru Pastel</t>
+  </si>
+  <si>
+    <t>R379</t>
+  </si>
+  <si>
+    <t>351130045985</t>
+  </si>
+  <si>
+    <t>2133 Biru Benhur</t>
+  </si>
+  <si>
+    <t>2133</t>
+  </si>
+  <si>
+    <t>351130045987</t>
+  </si>
+  <si>
+    <t>904 Biru Toska</t>
+  </si>
+  <si>
+    <t>904</t>
+  </si>
+  <si>
+    <t>351130045989</t>
+  </si>
+  <si>
+    <t>855 Biru Wardah</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>351130045999</t>
+  </si>
+  <si>
+    <t>679 Biru Benhur</t>
+  </si>
+  <si>
+    <t>679</t>
+  </si>
+  <si>
+    <t>351130045982</t>
+  </si>
+  <si>
+    <t>004 Baby Blue</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>351130046002</t>
+  </si>
+  <si>
+    <t>308 Biru Tosca Muda</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
     <t>351130046000</t>
   </si>
   <si>
@@ -279,292 +471,118 @@
     <t>8910</t>
   </si>
   <si>
-    <t>00</t>
-  </si>
-  <si>
-    <t>351130045986</t>
-  </si>
-  <si>
-    <t>9085 Biru Langit</t>
-  </si>
-  <si>
-    <t>9085</t>
-  </si>
-  <si>
-    <t>351130045995</t>
-  </si>
-  <si>
-    <t>R379 Biru Pastel</t>
-  </si>
-  <si>
-    <t>R379</t>
-  </si>
-  <si>
-    <t>351130045985</t>
-  </si>
-  <si>
-    <t>2133 Biru Benhur</t>
-  </si>
-  <si>
-    <t>2133</t>
-  </si>
-  <si>
-    <t>351130045982</t>
-  </si>
-  <si>
-    <t>004 Baby Blue</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>351130045999</t>
-  </si>
-  <si>
-    <t>679 Biru Benhur</t>
-  </si>
-  <si>
-    <t>679</t>
-  </si>
-  <si>
-    <t>351130045983</t>
-  </si>
-  <si>
-    <t>2084 Biru Langit</t>
-  </si>
-  <si>
-    <t>2084</t>
-  </si>
-  <si>
-    <t>351130045987</t>
-  </si>
-  <si>
-    <t>904 Biru Toska</t>
-  </si>
-  <si>
-    <t>904</t>
-  </si>
-  <si>
-    <t>351130045992</t>
-  </si>
-  <si>
-    <t>8049 Baby Blue</t>
-  </si>
-  <si>
-    <t>8049</t>
-  </si>
-  <si>
-    <t>351130045991</t>
-  </si>
-  <si>
-    <t>R205 Biru Emerlad</t>
-  </si>
-  <si>
-    <t>R205</t>
-  </si>
-  <si>
-    <t>351130045998</t>
-  </si>
-  <si>
-    <t>CB Turkish Tua</t>
-  </si>
-  <si>
-    <t>CB</t>
-  </si>
-  <si>
-    <t>351130045994</t>
-  </si>
-  <si>
-    <t>138 Biru Muda</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>351130046002</t>
-  </si>
-  <si>
-    <t>308 Biru Tosca Muda</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>351130045990</t>
-  </si>
-  <si>
-    <t>R530 Dusty Blue</t>
-  </si>
-  <si>
-    <t>R530</t>
-  </si>
-  <si>
-    <t>351130045984</t>
-  </si>
-  <si>
-    <t>R274 Biru Russian</t>
-  </si>
-  <si>
-    <t>R274</t>
-  </si>
-  <si>
-    <t>351130046003</t>
-  </si>
-  <si>
-    <t>R532 Biru Emerld</t>
-  </si>
-  <si>
-    <t>R532</t>
-  </si>
-  <si>
-    <t>351130045989</t>
-  </si>
-  <si>
-    <t>855 Biru Wardah</t>
-  </si>
-  <si>
-    <t>855</t>
-  </si>
-  <si>
-    <t>351130046001</t>
-  </si>
-  <si>
-    <t>055 Biru Navy</t>
-  </si>
-  <si>
-    <t>055</t>
-  </si>
-  <si>
-    <t>351130045997</t>
-  </si>
-  <si>
-    <t>R533 Biru pearl</t>
-  </si>
-  <si>
-    <t>R533</t>
-  </si>
-  <si>
-    <t>351130045988</t>
-  </si>
-  <si>
-    <t>035 Biru Tua</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
-    <t>351130045993</t>
-  </si>
-  <si>
-    <t>8080 Blue</t>
-  </si>
-  <si>
-    <t>8080</t>
-  </si>
-  <si>
-    <t>351130045996</t>
-  </si>
-  <si>
-    <t>8805 Biru Turkis</t>
-  </si>
-  <si>
-    <t>8805</t>
-  </si>
-  <si>
     <t>52314467125</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Ungu | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>391245090182</t>
+  </si>
+  <si>
+    <t>8839 Lilac</t>
+  </si>
+  <si>
+    <t>391245090193</t>
+  </si>
+  <si>
+    <t>R516 Ungu Muda</t>
+  </si>
+  <si>
+    <t>391245090187</t>
+  </si>
+  <si>
+    <t>2241 Ungu Lolipop</t>
+  </si>
+  <si>
+    <t>391245090180</t>
+  </si>
+  <si>
+    <t>R509 Dusty Purple</t>
+  </si>
+  <si>
+    <t>391245090178</t>
+  </si>
+  <si>
+    <t>R500 Ungu Tua</t>
+  </si>
+  <si>
+    <t>391245090188</t>
+  </si>
+  <si>
+    <t>8824 Ungu Royal</t>
+  </si>
+  <si>
     <t>391245090176</t>
   </si>
   <si>
     <t>8826 Ungu Muda</t>
   </si>
   <si>
+    <t>391245090190</t>
+  </si>
+  <si>
+    <t>4664 Lavender</t>
+  </si>
+  <si>
+    <t>391245090191</t>
+  </si>
+  <si>
+    <t>012 Ungu</t>
+  </si>
+  <si>
+    <t>391245090192</t>
+  </si>
+  <si>
+    <t>787 Biru Ungu</t>
+  </si>
+  <si>
+    <t>391245090175</t>
+  </si>
+  <si>
+    <t>R520 Mulberry</t>
+  </si>
+  <si>
+    <t>391245090185</t>
+  </si>
+  <si>
+    <t>2160 Coklat Ungu</t>
+  </si>
+  <si>
+    <t>391245090179</t>
+  </si>
+  <si>
+    <t>700 Dusty Purple</t>
+  </si>
+  <si>
+    <t>391245090181</t>
+  </si>
+  <si>
+    <t>R510 Dusty Ungu</t>
+  </si>
+  <si>
+    <t>391245090183</t>
+  </si>
+  <si>
+    <t>4701 Pink Ungu</t>
+  </si>
+  <si>
     <t>391245090189</t>
   </si>
   <si>
     <t>8803 Ungu Tua</t>
   </si>
   <si>
-    <t>391245090185</t>
-  </si>
-  <si>
-    <t>2160 Coklat Ungu</t>
-  </si>
-  <si>
-    <t>391245090175</t>
-  </si>
-  <si>
-    <t>R520 Mulberry</t>
-  </si>
-  <si>
     <t>391245090177</t>
   </si>
   <si>
     <t>R503 Ungu Terong</t>
   </si>
   <si>
-    <t>391245090183</t>
-  </si>
-  <si>
-    <t>4701 Pink Ungu</t>
-  </si>
-  <si>
-    <t>391245090181</t>
-  </si>
-  <si>
-    <t>R510 Dusty Ungu</t>
-  </si>
-  <si>
-    <t>391245090179</t>
-  </si>
-  <si>
-    <t>700 Dusty Purple</t>
-  </si>
-  <si>
-    <t>391245090193</t>
-  </si>
-  <si>
-    <t>R516 Ungu Muda</t>
-  </si>
-  <si>
-    <t>391245090187</t>
-  </si>
-  <si>
-    <t>2241 Ungu Lolipop</t>
-  </si>
-  <si>
-    <t>391245090190</t>
-  </si>
-  <si>
-    <t>4664 Lavender</t>
-  </si>
-  <si>
-    <t>391245090191</t>
-  </si>
-  <si>
-    <t>012 Ungu</t>
-  </si>
-  <si>
-    <t>391245090178</t>
-  </si>
-  <si>
-    <t>R500 Ungu Tua</t>
-  </si>
-  <si>
-    <t>391245090192</t>
-  </si>
-  <si>
-    <t>787 Biru Ungu</t>
-  </si>
-  <si>
-    <t>391245090180</t>
-  </si>
-  <si>
-    <t>R509 Dusty Purple</t>
+    <t>391245090184</t>
+  </si>
+  <si>
+    <t>2360 Ungu Plum</t>
   </si>
   <si>
     <t>391245090186</t>
@@ -573,34 +591,16 @@
     <t>R364 Dusty Purple</t>
   </si>
   <si>
-    <t>391245090184</t>
-  </si>
-  <si>
-    <t>2360 Ungu Plum</t>
-  </si>
-  <si>
-    <t>391245090182</t>
-  </si>
-  <si>
-    <t>8839 Lilac</t>
-  </si>
-  <si>
-    <t>391245090188</t>
-  </si>
-  <si>
-    <t>8824 Ungu Royal</t>
-  </si>
-  <si>
     <t>48413080166</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Kuning | Benang Obras Konveksi</t>
   </si>
   <si>
-    <t>356131775592</t>
-  </si>
-  <si>
-    <t>2032 Kuning</t>
+    <t>356131775586</t>
+  </si>
+  <si>
+    <t>8848 Kuning Kenari</t>
   </si>
   <si>
     <t>356131775584</t>
@@ -609,76 +609,76 @@
     <t>786 Dark Yellow</t>
   </si>
   <si>
+    <t>356131775590</t>
+  </si>
+  <si>
+    <t>2196 Kuning Kunyit</t>
+  </si>
+  <si>
+    <t>356131775591</t>
+  </si>
+  <si>
+    <t>412 Krem Kuning</t>
+  </si>
+  <si>
+    <t>356131775580</t>
+  </si>
+  <si>
+    <t>9261 Khaki</t>
+  </si>
+  <si>
+    <t>356131775593</t>
+  </si>
+  <si>
+    <t>1626 Kuning</t>
+  </si>
+  <si>
+    <t>356131775588</t>
+  </si>
+  <si>
+    <t>R170 Gold</t>
+  </si>
+  <si>
+    <t>356131775585</t>
+  </si>
+  <si>
+    <t>203B Kuning Gading</t>
+  </si>
+  <si>
+    <t>356131775579</t>
+  </si>
+  <si>
+    <t>2166 Stabilo</t>
+  </si>
+  <si>
+    <t>356131775587</t>
+  </si>
+  <si>
+    <t>9351 Mustard</t>
+  </si>
+  <si>
     <t>356131775583</t>
   </si>
   <si>
     <t>4671 Kunyit</t>
   </si>
   <si>
+    <t>356131775589</t>
+  </si>
+  <si>
+    <t>R304 Khaki</t>
+  </si>
+  <si>
     <t>356131775578</t>
   </si>
   <si>
     <t>9293 Kuning Royal</t>
   </si>
   <si>
-    <t>356131775593</t>
-  </si>
-  <si>
-    <t>1626 Kuning</t>
-  </si>
-  <si>
-    <t>356131775587</t>
-  </si>
-  <si>
-    <t>9351 Mustard</t>
-  </si>
-  <si>
-    <t>356131775589</t>
-  </si>
-  <si>
-    <t>R304 Khaki</t>
-  </si>
-  <si>
-    <t>356131775591</t>
-  </si>
-  <si>
-    <t>412 Krem Kuning</t>
-  </si>
-  <si>
-    <t>356131775586</t>
-  </si>
-  <si>
-    <t>8848 Kuning Kenari</t>
-  </si>
-  <si>
-    <t>356131775579</t>
-  </si>
-  <si>
-    <t>2166 Stabilo</t>
-  </si>
-  <si>
-    <t>356131775585</t>
-  </si>
-  <si>
-    <t>203B Kuning Gading</t>
-  </si>
-  <si>
-    <t>356131775590</t>
-  </si>
-  <si>
-    <t>2196 Kuning Kunyit</t>
-  </si>
-  <si>
-    <t>356131775580</t>
-  </si>
-  <si>
-    <t>9261 Khaki</t>
-  </si>
-  <si>
-    <t>356131775588</t>
-  </si>
-  <si>
-    <t>R170 Gold</t>
+    <t>356131775582</t>
+  </si>
+  <si>
+    <t>9218 Kuning Muda</t>
   </si>
   <si>
     <t>356131775581</t>
@@ -687,18 +687,48 @@
     <t>7955 Kuning</t>
   </si>
   <si>
-    <t>356131775582</t>
-  </si>
-  <si>
-    <t>9218 Kuning Muda</t>
-  </si>
-  <si>
     <t>47863030679</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Abu | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>351127388075</t>
+  </si>
+  <si>
+    <t>9213 Abu Tua</t>
+  </si>
+  <si>
+    <t>9213</t>
+  </si>
+  <si>
+    <t>351127388076</t>
+  </si>
+  <si>
+    <t>7610 Abu Tua</t>
+  </si>
+  <si>
+    <t>7610</t>
+  </si>
+  <si>
+    <t>351127388077</t>
+  </si>
+  <si>
+    <t>109 Abu Abu</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>351127388070</t>
+  </si>
+  <si>
+    <t>110 Abu SMA</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>351127388071</t>
   </si>
   <si>
@@ -738,48 +768,30 @@
     <t>111</t>
   </si>
   <si>
-    <t>351127388075</t>
-  </si>
-  <si>
-    <t>9213 Abu Tua</t>
-  </si>
-  <si>
-    <t>9213</t>
-  </si>
-  <si>
-    <t>351127388076</t>
-  </si>
-  <si>
-    <t>7610 Abu Tua</t>
-  </si>
-  <si>
-    <t>7610</t>
-  </si>
-  <si>
-    <t>351127388077</t>
-  </si>
-  <si>
-    <t>109 Abu Abu</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>351127388070</t>
-  </si>
-  <si>
-    <t>110 Abu SMA</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>46214486708</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Merah | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>316245541304</t>
+  </si>
+  <si>
+    <t>8874 Merah SD</t>
+  </si>
+  <si>
+    <t>316245541298</t>
+  </si>
+  <si>
+    <t>7807 Merah Tua</t>
+  </si>
+  <si>
+    <t>316245541299</t>
+  </si>
+  <si>
+    <t>791Terakota</t>
+  </si>
+  <si>
     <t>316245541300</t>
   </si>
   <si>
@@ -804,30 +816,30 @@
     <t>R143 Merah Coklat</t>
   </si>
   <si>
-    <t>316245541304</t>
-  </si>
-  <si>
-    <t>8874 Merah SD</t>
-  </si>
-  <si>
-    <t>316245541298</t>
-  </si>
-  <si>
-    <t>7807 Merah Tua</t>
-  </si>
-  <si>
-    <t>316245541299</t>
-  </si>
-  <si>
-    <t>791Terakota</t>
-  </si>
-  <si>
     <t>44913065678</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Hijau | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>356130916187</t>
+  </si>
+  <si>
+    <t>532 Hijau Pupus</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>356130916198</t>
+  </si>
+  <si>
+    <t>4566 Hijau Sage</t>
+  </si>
+  <si>
+    <t>4566</t>
+  </si>
+  <si>
     <t>356130916205</t>
   </si>
   <si>
@@ -837,6 +849,15 @@
     <t>2154</t>
   </si>
   <si>
+    <t>356130916196</t>
+  </si>
+  <si>
+    <t>030 Hijau Muda</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
     <t>356130916211</t>
   </si>
   <si>
@@ -846,6 +867,168 @@
     <t>072</t>
   </si>
   <si>
+    <t>356130916193</t>
+  </si>
+  <si>
+    <t>8847 Hijau Sage</t>
+  </si>
+  <si>
+    <t>8847</t>
+  </si>
+  <si>
+    <t>356130916209</t>
+  </si>
+  <si>
+    <t>R328 Hijau Muda</t>
+  </si>
+  <si>
+    <t>R328</t>
+  </si>
+  <si>
+    <t>356130916203</t>
+  </si>
+  <si>
+    <t>R406 Khaki Hijau</t>
+  </si>
+  <si>
+    <t>R406</t>
+  </si>
+  <si>
+    <t>356130916207</t>
+  </si>
+  <si>
+    <t>R494 Toska</t>
+  </si>
+  <si>
+    <t>R494</t>
+  </si>
+  <si>
+    <t>356130916191</t>
+  </si>
+  <si>
+    <t>2116 Tosca</t>
+  </si>
+  <si>
+    <t>2116</t>
+  </si>
+  <si>
+    <t>356130916192</t>
+  </si>
+  <si>
+    <t>8878 Hijau Mint</t>
+  </si>
+  <si>
+    <t>8878</t>
+  </si>
+  <si>
+    <t>356130916184</t>
+  </si>
+  <si>
+    <t>8843 Hijau Mint</t>
+  </si>
+  <si>
+    <t>8843</t>
+  </si>
+  <si>
+    <t>356130916197</t>
+  </si>
+  <si>
+    <t>2582 Hijau Sage</t>
+  </si>
+  <si>
+    <t>2582</t>
+  </si>
+  <si>
+    <t>356130916202</t>
+  </si>
+  <si>
+    <t>862 Teal</t>
+  </si>
+  <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>356130916204</t>
+  </si>
+  <si>
+    <t>7910 Hijau Lumut</t>
+  </si>
+  <si>
+    <t>7910</t>
+  </si>
+  <si>
+    <t>356130916186</t>
+  </si>
+  <si>
+    <t>R484 Hijau Lumut</t>
+  </si>
+  <si>
+    <t>R484</t>
+  </si>
+  <si>
+    <t>356130916200</t>
+  </si>
+  <si>
+    <t>R206 Hijau Tua</t>
+  </si>
+  <si>
+    <t>R206</t>
+  </si>
+  <si>
+    <t>356130916188</t>
+  </si>
+  <si>
+    <t>R400 Hijau Botol</t>
+  </si>
+  <si>
+    <t>R400</t>
+  </si>
+  <si>
+    <t>356130916190</t>
+  </si>
+  <si>
+    <t>215 Hijau SeaWeed</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>356130916195</t>
+  </si>
+  <si>
+    <t>448 Hijau Daun</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>356130916206</t>
+  </si>
+  <si>
+    <t>819 Hijau Muda</t>
+  </si>
+  <si>
+    <t>819</t>
+  </si>
+  <si>
+    <t>356130916201</t>
+  </si>
+  <si>
+    <t>7905 Hjau Cerah</t>
+  </si>
+  <si>
+    <t>7905</t>
+  </si>
+  <si>
+    <t>356130916194</t>
+  </si>
+  <si>
+    <t>032 Hijau Daun</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
     <t>356130916208</t>
   </si>
   <si>
@@ -855,31 +1038,40 @@
     <t>1660</t>
   </si>
   <si>
-    <t>356130916191</t>
-  </si>
-  <si>
-    <t>2116 Tosca</t>
-  </si>
-  <si>
-    <t>2116</t>
-  </si>
-  <si>
-    <t>356130916209</t>
-  </si>
-  <si>
-    <t>R328 Hijau Muda</t>
-  </si>
-  <si>
-    <t>R328</t>
-  </si>
-  <si>
-    <t>356130916207</t>
-  </si>
-  <si>
-    <t>R494 Toska</t>
-  </si>
-  <si>
-    <t>R494</t>
+    <t>356130916189</t>
+  </si>
+  <si>
+    <t>2685 Hijau Sage Muda</t>
+  </si>
+  <si>
+    <t>2685</t>
+  </si>
+  <si>
+    <t>356130916185</t>
+  </si>
+  <si>
+    <t>353 Hijau Emerald</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>356130916210</t>
+  </si>
+  <si>
+    <t>860 Hijau</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>356130916199</t>
+  </si>
+  <si>
+    <t>8833 Hijau Tosca</t>
+  </si>
+  <si>
+    <t>8833</t>
   </si>
   <si>
     <t>356130916212</t>
@@ -891,252 +1083,144 @@
     <t>8863</t>
   </si>
   <si>
-    <t>356130916198</t>
-  </si>
-  <si>
-    <t>4566 Hijau Sage</t>
-  </si>
-  <si>
-    <t>4566</t>
-  </si>
-  <si>
-    <t>356130916188</t>
-  </si>
-  <si>
-    <t>R400 Hijau Botol</t>
-  </si>
-  <si>
-    <t>R400</t>
-  </si>
-  <si>
-    <t>356130916186</t>
-  </si>
-  <si>
-    <t>R484 Hijau Lumut</t>
-  </si>
-  <si>
-    <t>R484</t>
-  </si>
-  <si>
-    <t>356130916193</t>
-  </si>
-  <si>
-    <t>8847 Hijau Sage</t>
-  </si>
-  <si>
-    <t>8847</t>
-  </si>
-  <si>
-    <t>356130916194</t>
-  </si>
-  <si>
-    <t>032 Hijau Daun</t>
-  </si>
-  <si>
-    <t>032</t>
-  </si>
-  <si>
-    <t>356130916184</t>
-  </si>
-  <si>
-    <t>8843 Hijau Mint</t>
-  </si>
-  <si>
-    <t>8843</t>
-  </si>
-  <si>
-    <t>356130916192</t>
-  </si>
-  <si>
-    <t>8878 Hijau Mint</t>
-  </si>
-  <si>
-    <t>8878</t>
-  </si>
-  <si>
-    <t>356130916203</t>
-  </si>
-  <si>
-    <t>R406 Khaki Hijau</t>
-  </si>
-  <si>
-    <t>R406</t>
-  </si>
-  <si>
-    <t>356130916187</t>
-  </si>
-  <si>
-    <t>532 Hijau Pupus</t>
-  </si>
-  <si>
-    <t>532</t>
-  </si>
-  <si>
-    <t>356130916197</t>
-  </si>
-  <si>
-    <t>2582 Hijau Sage</t>
-  </si>
-  <si>
-    <t>2582</t>
-  </si>
-  <si>
-    <t>356130916190</t>
-  </si>
-  <si>
-    <t>215 Hijau SeaWeed</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>356130916206</t>
-  </si>
-  <si>
-    <t>819 Hijau Muda</t>
-  </si>
-  <si>
-    <t>819</t>
-  </si>
-  <si>
-    <t>356130916204</t>
-  </si>
-  <si>
-    <t>7910 Hijau Lumut</t>
-  </si>
-  <si>
-    <t>7910</t>
-  </si>
-  <si>
-    <t>356130916185</t>
-  </si>
-  <si>
-    <t>353 Hijau Emerald</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>356130916200</t>
-  </si>
-  <si>
-    <t>R206 Hijau Tua</t>
-  </si>
-  <si>
-    <t>R206</t>
-  </si>
-  <si>
-    <t>356130916210</t>
-  </si>
-  <si>
-    <t>860 Hijau</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>356130916196</t>
-  </si>
-  <si>
-    <t>030 Hijau Muda</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
-    <t>356130916195</t>
-  </si>
-  <si>
-    <t>448 Hijau Daun</t>
-  </si>
-  <si>
-    <t>448</t>
-  </si>
-  <si>
-    <t>356130916199</t>
-  </si>
-  <si>
-    <t>8833 Hijau Tosca</t>
-  </si>
-  <si>
-    <t>8833</t>
-  </si>
-  <si>
-    <t>356130916202</t>
-  </si>
-  <si>
-    <t>862 Teal</t>
-  </si>
-  <si>
-    <t>862</t>
-  </si>
-  <si>
-    <t>356130916189</t>
-  </si>
-  <si>
-    <t>2685 Hijau Sage Muda</t>
-  </si>
-  <si>
-    <t>2685</t>
-  </si>
-  <si>
-    <t>356130916201</t>
-  </si>
-  <si>
-    <t>7905 Hjau Cerah</t>
-  </si>
-  <si>
-    <t>7905</t>
-  </si>
-  <si>
     <t>43182804641</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Orange | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>331244974018</t>
+  </si>
+  <si>
+    <t>8068 Cantaloupe</t>
+  </si>
+  <si>
+    <t>331244974019</t>
+  </si>
+  <si>
+    <t>457/8868 Fanta</t>
+  </si>
+  <si>
+    <t>331244974020</t>
+  </si>
+  <si>
+    <t>8861 Orange</t>
+  </si>
+  <si>
+    <t>331244974021</t>
+  </si>
+  <si>
+    <t>079 Orange Carrot</t>
+  </si>
+  <si>
+    <t>331244974022</t>
+  </si>
+  <si>
+    <t>101 Orange Sherbert</t>
+  </si>
+  <si>
     <t>331244974017</t>
   </si>
   <si>
     <t>R210 Salem Orange</t>
   </si>
   <si>
-    <t>331244974018</t>
-  </si>
-  <si>
-    <t>8068 Cantaloupe</t>
-  </si>
-  <si>
-    <t>331244974019</t>
-  </si>
-  <si>
-    <t>457/8868 Fanta</t>
-  </si>
-  <si>
-    <t>331244974020</t>
-  </si>
-  <si>
-    <t>8861 Orange</t>
-  </si>
-  <si>
-    <t>331244974021</t>
-  </si>
-  <si>
-    <t>079 Orange Carrot</t>
-  </si>
-  <si>
-    <t>331244974022</t>
-  </si>
-  <si>
-    <t>101 Orange Sherbert</t>
-  </si>
-  <si>
     <t>41332113600</t>
   </si>
   <si>
     <t>Benang Obras Ivory 2 Ons Kategori Coklat | Benang Obras Konveksi</t>
   </si>
   <si>
+    <t>297738563677</t>
+  </si>
+  <si>
+    <t>R178 Krem Putih</t>
+  </si>
+  <si>
+    <t>R178</t>
+  </si>
+  <si>
+    <t>297738563686</t>
+  </si>
+  <si>
+    <t>189 Taupe</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>297738563674</t>
+  </si>
+  <si>
+    <t>A71 Coklat Susu</t>
+  </si>
+  <si>
+    <t>A71</t>
+  </si>
+  <si>
+    <t>297738563688</t>
+  </si>
+  <si>
+    <t>616 Beige</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>297738563679</t>
+  </si>
+  <si>
+    <t>2003 Coklat Abu</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>297738563683</t>
+  </si>
+  <si>
+    <t>R242 Mocca</t>
+  </si>
+  <si>
+    <t>R242</t>
+  </si>
+  <si>
+    <t>297738563682</t>
+  </si>
+  <si>
+    <t>G24/2115 Mocca</t>
+  </si>
+  <si>
+    <t>2115</t>
+  </si>
+  <si>
+    <t>297738563689</t>
+  </si>
+  <si>
+    <t>686A Coklat Tua</t>
+  </si>
+  <si>
+    <t>686A</t>
+  </si>
+  <si>
+    <t>297738563680</t>
+  </si>
+  <si>
+    <t>R236 Coklat Bronze</t>
+  </si>
+  <si>
+    <t>R236</t>
+  </si>
+  <si>
+    <t>297738563676</t>
+  </si>
+  <si>
+    <t>677 Coklat Tua</t>
+  </si>
+  <si>
+    <t>677</t>
+  </si>
+  <si>
     <t>297738563678</t>
   </si>
   <si>
@@ -1155,31 +1239,13 @@
     <t>7607</t>
   </si>
   <si>
-    <t>297738563683</t>
-  </si>
-  <si>
-    <t>R242 Mocca</t>
-  </si>
-  <si>
-    <t>R242</t>
-  </si>
-  <si>
-    <t>297738563688</t>
-  </si>
-  <si>
-    <t>616 Beige</t>
-  </si>
-  <si>
-    <t>616</t>
-  </si>
-  <si>
-    <t>297738563679</t>
-  </si>
-  <si>
-    <t>2003 Coklat Abu</t>
-  </si>
-  <si>
-    <t>2003</t>
+    <t>297738563685</t>
+  </si>
+  <si>
+    <t>8928 Krem</t>
+  </si>
+  <si>
+    <t>8928</t>
   </si>
   <si>
     <t>297738563691</t>
@@ -1191,49 +1257,31 @@
     <t>753B</t>
   </si>
   <si>
-    <t>297738563674</t>
-  </si>
-  <si>
-    <t>A71 Coklat Susu</t>
-  </si>
-  <si>
-    <t>A71</t>
-  </si>
-  <si>
-    <t>297738563689</t>
-  </si>
-  <si>
-    <t>686A Coklat Tua</t>
-  </si>
-  <si>
-    <t>686A</t>
-  </si>
-  <si>
-    <t>297738563686</t>
-  </si>
-  <si>
-    <t>189 Taupe</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>297738563680</t>
-  </si>
-  <si>
-    <t>R236 Coklat Bronze</t>
-  </si>
-  <si>
-    <t>R236</t>
-  </si>
-  <si>
-    <t>297738563676</t>
-  </si>
-  <si>
-    <t>677 Coklat Tua</t>
-  </si>
-  <si>
-    <t>677</t>
+    <t>297738563675</t>
+  </si>
+  <si>
+    <t>593 Coklat Tan</t>
+  </si>
+  <si>
+    <t>593</t>
+  </si>
+  <si>
+    <t>297738563687</t>
+  </si>
+  <si>
+    <t>2088 Atasan Pramuka</t>
+  </si>
+  <si>
+    <t>2088</t>
+  </si>
+  <si>
+    <t>297738563690</t>
+  </si>
+  <si>
+    <t>085 Coklat Kopi</t>
+  </si>
+  <si>
+    <t>085</t>
   </si>
   <si>
     <t>297738563681</t>
@@ -1243,60 +1291,6 @@
   </si>
   <si>
     <t>7602</t>
-  </si>
-  <si>
-    <t>297738563690</t>
-  </si>
-  <si>
-    <t>085 Coklat Kopi</t>
-  </si>
-  <si>
-    <t>085</t>
-  </si>
-  <si>
-    <t>297738563685</t>
-  </si>
-  <si>
-    <t>8928 Krem</t>
-  </si>
-  <si>
-    <t>8928</t>
-  </si>
-  <si>
-    <t>297738563687</t>
-  </si>
-  <si>
-    <t>2088 Atasan Pramuka</t>
-  </si>
-  <si>
-    <t>2088</t>
-  </si>
-  <si>
-    <t>297738563675</t>
-  </si>
-  <si>
-    <t>593 Coklat Tan</t>
-  </si>
-  <si>
-    <t>593</t>
-  </si>
-  <si>
-    <t>297738563677</t>
-  </si>
-  <si>
-    <t>R178 Krem Putih</t>
-  </si>
-  <si>
-    <t>R178</t>
-  </si>
-  <si>
-    <t>297738563682</t>
-  </si>
-  <si>
-    <t>G24/2115 Mocca</t>
-  </si>
-  <si>
-    <t>2115</t>
   </si>
 </sst>
 </file>
